--- a/Subcorpora_Welsh.xlsx
+++ b/Subcorpora_Welsh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jamesbutler/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CB6CE4-7DDF-714F-BAF1-C8EBE56620C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDFF251-7F27-DE42-AF7E-5CE67A83E75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{5820E604-842D-DE4E-8FE2-EBAD569F3969}"/>
   </bookViews>
